--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/sep-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/sep-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC sep-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC sep-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6295,7 +6295,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6905,7 +6905,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8369,7 +8369,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9040,7 +9040,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9345,7 +9345,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10565,7 +10565,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10687,7 +10687,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10702,7 +10702,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/sep-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/sep-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M174"/>
+  <dimension ref="A1:M176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1273,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1399,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1464,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1529,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1594,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1659,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1724,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1850,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1915,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1980,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2045,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2110,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2175,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2240,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2366,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2431,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2496,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2561,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2626,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2752,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2817,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2882,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2884,7 +3012,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2945,7 +3077,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3203,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3128,7 +3268,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3333,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3250,7 +3398,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3433,7 +3585,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3494,7 +3650,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3555,7 +3715,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3568,7 +3732,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>858-472-CM25</t>
+          <t>2961-650-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3593,12 +3757,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.072.400-6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LA GRANJA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3608,28 +3772,32 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>35071.68</v>
+        <v>5852.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2547-332-CM25</t>
+          <t>1393093-1124-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3649,22 +3817,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3677,20 +3845,24 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>5330.72</v>
+        <v>53444.84</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2961-650-CM25</t>
+          <t>858-472-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3715,12 +3887,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.072.400-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA GRANJA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3730,28 +3902,32 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>5852.9</v>
+        <v>35071.68</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1393093-1124-CM25</t>
+          <t>2547-332-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3771,22 +3947,22 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3799,20 +3975,24 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>53444.84</v>
+        <v>5330.72</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3495-191-CM25</t>
+          <t>3305-530-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3832,48 +4012,52 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>69.141.801-4</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>I MUNICIPALIDAD DE TUCAPEL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>7306.6</v>
+        <v>5183.64</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4404-298-CM25</t>
+          <t>3495-191-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3893,48 +4077,52 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>25995.48</v>
+        <v>7306.6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1224957-1053-CM25</t>
+          <t>4404-298-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3959,43 +4147,47 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>70.932.800-K</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE NUNOA</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>6481.41</v>
+        <v>25995.48</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3305-530-CM25</t>
+          <t>1224957-1053-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4020,37 +4212,41 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.141.801-4</t>
+          <t>70.932.800-K</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TUCAPEL</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE NUNOA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5183.64</v>
+        <v>6481.41</v>
       </c>
     </row>
     <row r="60">
@@ -4104,7 +4300,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4165,7 +4365,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4178,7 +4382,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1274189-384-CM25</t>
+          <t>514847-1227-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4198,48 +4402,52 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>70.934.900-7</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>CORPORACION DE DESARROLLO SOCIAL DE BUIN</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>10249.29</v>
+        <v>16271.92</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1288-414-CM25</t>
+          <t>1274189-384-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4259,17 +4467,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>70.934.900-7</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>CORPORACION DE DESARROLLO SOCIAL DE BUIN</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4279,32 +4487,28 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.596.570-5</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>69261.57000000001</v>
+        <v>10249.29</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1180885-7-CM25</t>
+          <t>1288-414-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4324,22 +4528,22 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4363,13 +4567,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>89178.60000000001</v>
+        <v>69261.57000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>514847-1227-CM25</t>
+          <t>1180885-7-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4389,48 +4593,52 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>16271.92</v>
+        <v>89178.60000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3858-396-CM25</t>
+          <t>3767-186-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4450,48 +4658,52 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>8091.17</v>
+        <v>13695.23</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3767-186-CM25</t>
+          <t>1126922-1812-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4516,43 +4728,47 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>13695.23</v>
+        <v>14031.29</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1126922-1812-CM25</t>
+          <t>4573-28-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4577,43 +4793,47 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>69.061.100-7</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>I MUNICIPALIDAD DE LIMACHE</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>14031.29</v>
+        <v>4180.76</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4573-28-CM25</t>
+          <t>85-299-CC25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4638,43 +4858,47 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.061.100-7</t>
+          <t>60.908.000-0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LIMACHE</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>4180.76</v>
+        <v>87497.89999999999</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2421-4367-CM25</t>
+          <t>3858-396-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4694,48 +4918,52 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.256.900-8</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>8615.360000000001</v>
+        <v>8091.17</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>586-466-CM25</t>
+          <t>4928-79-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4755,48 +4983,52 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>22438.64</v>
+        <v>3005.76</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2274-235-CM25</t>
+          <t>586-466-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4816,48 +5048,52 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.253.800-5</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA PINTANA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>10195.03</v>
+        <v>22438.64</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4928-77-CM25</t>
+          <t>2274-235-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4882,12 +5118,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.253.800-5</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LA PINTANA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4897,28 +5133,32 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>16736.45</v>
+        <v>10195.03</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1417913-171-CM25</t>
+          <t>4928-77-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4938,48 +5178,52 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>70.938.800-2</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>3617.55</v>
+        <v>16736.45</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4928-79-CM25</t>
+          <t>1417913-171-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4999,48 +5243,52 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>3005.76</v>
+        <v>3617.55</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2429-2579-CM25</t>
+          <t>2421-4367-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5055,53 +5303,57 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.256.900-8</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>7754.04</v>
+        <v>8615.360000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2445-3428-CM25</t>
+          <t>2429-2579-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5121,48 +5373,52 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>65464.52</v>
+        <v>7754.04</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1432083-1224-CM25</t>
+          <t>2445-3428-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5187,27 +5443,27 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5217,7 +5473,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>4053.97</v>
+        <v>65464.52</v>
       </c>
     </row>
     <row r="79">
@@ -5271,7 +5527,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5284,7 +5544,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1126922-1804-CM25</t>
+          <t>1432083-1224-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5309,43 +5569,47 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>19768.28</v>
+        <v>4053.97</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2448-725-CM25</t>
+          <t>1126922-1804-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5370,43 +5634,47 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>12939.7</v>
+        <v>19768.28</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5178-4230-CM25</t>
+          <t>2448-725-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5431,43 +5699,47 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>3003.52</v>
+        <v>12939.7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2305-66-CM25</t>
+          <t>5178-4230-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5482,7 +5754,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5492,12 +5764,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.973.000-3</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>UNIDAD DE ANALISIS FINANCIERO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5507,28 +5779,32 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>17403.16</v>
+        <v>3003.52</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5872-178-CM25</t>
+          <t>2305-66-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5553,12 +5829,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.973.000-3</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIDAD DE ANALISIS FINANCIERO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5568,28 +5844,32 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>23145.5</v>
+        <v>17403.16</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2780-432-CM25</t>
+          <t>5872-178-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5614,43 +5894,47 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.050.100-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>16012.88</v>
+        <v>23145.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2305-67-CM25</t>
+          <t>2780-432-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5675,17 +5959,17 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.973.000-3</t>
+          <t>69.050.100-7</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>UNIDAD DE ANALISIS FINANCIERO</t>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5698,20 +5982,24 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>4176.76</v>
+        <v>16012.88</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2780-431-CM25</t>
+          <t>2305-67-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5731,48 +6019,52 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>69.050.100-7</t>
+          <t>61.973.000-3</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+          <t>UNIDAD DE ANALISIS FINANCIERO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>8339.379999999999</v>
+        <v>4176.76</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2778-785-CM25</t>
+          <t>2780-431-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5797,43 +6089,47 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.050.100-7</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2765.56</v>
+        <v>8339.379999999999</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3871-248-CM25</t>
+          <t>2778-785-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5858,43 +6154,47 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>72.632.100-0</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PEMUCO</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>4339.1</v>
+        <v>2765.56</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3871-247-CM25</t>
+          <t>3871-248-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5949,13 +6249,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>3659.25</v>
+        <v>4339.1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4205-294-CM25</t>
+          <t>3191-4719-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5975,48 +6275,52 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>69.073.900-3</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAVI</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>6429.62</v>
+        <v>4241.06</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1658-4322-CM25</t>
+          <t>3871-247-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6041,17 +6345,17 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>72.632.100-0</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE PEMUCO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6071,13 +6375,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>11890.24</v>
+        <v>3659.25</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1216085-446-CM25</t>
+          <t>4205-294-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6102,43 +6406,47 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>70.983.600-5</t>
+          <t>69.073.900-3</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL PARA EL DESARROLLO SOCIAL</t>
+          <t>I MUNICIPALIDAD DE CURACAVI</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>4083.65</v>
+        <v>6429.62</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1216085-444-CM25</t>
+          <t>1658-4322-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6158,32 +6466,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>70.983.600-5</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL PARA EL DESARROLLO SOCIAL</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6193,13 +6501,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>4663.61</v>
+        <v>11890.24</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3191-4719-CM25</t>
+          <t>1216085-446-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6219,17 +6527,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>70.983.600-5</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>CORP MUNICIPAL PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6239,28 +6547,32 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>4241.06</v>
+        <v>4083.65</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4561-111-CM25</t>
+          <t>1216085-444-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6275,7 +6587,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6285,12 +6597,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>69.050.200-3</t>
+          <t>70.983.600-5</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABILDO</t>
+          <t>CORP MUNICIPAL PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6300,28 +6612,32 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>8385.82</v>
+        <v>4663.61</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1224957-1063-CM25</t>
+          <t>4561-111-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6341,32 +6657,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>70.932.800-K</t>
+          <t>69.050.200-3</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE NUNOA</t>
+          <t>I MUNICIPALIDAD DE CABILDO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6376,13 +6692,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>13803.52</v>
+        <v>8385.82</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3134-335-CM25</t>
+          <t>1224957-1063-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6402,48 +6718,52 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>70.932.800-K</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE NUNOA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>5107.96</v>
+        <v>13803.52</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>4374-97-CM25</t>
+          <t>3134-335-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6468,43 +6788,47 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>72.240.400-9</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2766.71</v>
+        <v>5107.96</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>976-294-CM25</t>
+          <t>4374-97-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6529,43 +6853,47 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>72.240.400-9</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>31921.31</v>
+        <v>2766.71</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1375760-28-CM25</t>
+          <t>976-294-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6580,7 +6908,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6590,12 +6918,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.981.310-3</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE CACHAPOAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6605,12 +6933,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6620,13 +6948,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>32854.35</v>
+        <v>31921.31</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1375760-27-CM25</t>
+          <t>1375760-28-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6666,12 +6994,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6681,7 +7009,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>3887.73</v>
+        <v>32854.35</v>
       </c>
     </row>
     <row r="103">
@@ -6735,7 +7063,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6796,7 +7128,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6809,7 +7145,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5148-142-CM25</t>
+          <t>1375760-27-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6834,12 +7170,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.981.310-3</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE CACHAPOAL</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6849,28 +7185,32 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>28383.11</v>
+        <v>3887.73</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3864-237-CM25</t>
+          <t>5148-142-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6890,48 +7230,52 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr"/>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>25195.99</v>
+        <v>28383.11</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4081-273-CM25</t>
+          <t>3864-237-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6956,43 +7300,47 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>69.151.001-8</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2374.05</v>
+        <v>25195.99</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2020-366-CM25</t>
+          <t>4081-273-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7007,7 +7355,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7017,43 +7365,47 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>60.203.000-8</t>
+          <t>69.151.001-8</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Biblioteca del Congreso Nacional</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>3401.02</v>
+        <v>2374.05</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2020-367-CM25</t>
+          <t>85-305-CC25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7068,22 +7420,22 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>60.203.000-8</t>
+          <t>60.908.000-0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Biblioteca del Congreso Nacional</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7093,28 +7445,32 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2222.92</v>
+        <v>34793.22</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1432083-1277-CM25</t>
+          <t>2020-366-CM25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7134,48 +7490,52 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>60.203.000-8</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>Biblioteca del Congreso Nacional</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>6198.71</v>
+        <v>3401.02</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2020-368-CM25</t>
+          <t>2020-367-CM25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7215,28 +7575,32 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>3786.15</v>
+        <v>2222.92</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1417913-305-CM25</t>
+          <t>1432083-1277-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7256,32 +7620,32 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>70.938.800-2</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7291,13 +7655,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>8945.129999999999</v>
+        <v>6198.71</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2803-265-CM25</t>
+          <t>2020-368-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7312,53 +7676,57 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>60.203.000-8</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>Biblioteca del Congreso Nacional</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>23529.87</v>
+        <v>3786.15</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>3614-293-CM25</t>
+          <t>1417913-305-CM25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7373,53 +7741,57 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>5987.01</v>
+        <v>8945.129999999999</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>603663-312-CM25</t>
+          <t>2803-265-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7444,43 +7816,47 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>65.028.707-K</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>2411.11</v>
+        <v>23529.87</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1110404-1263-CM25</t>
+          <t>3614-293-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7505,27 +7881,27 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7535,13 +7911,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>5272.81</v>
+        <v>5987.01</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>4284-459-CM25</t>
+          <t>603663-312-CM25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7566,43 +7942,47 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>65.028.707-K</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>5901.9</v>
+        <v>2411.11</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1469-2728-CM25</t>
+          <t>1110404-1263-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7617,53 +7997,57 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>18092.26</v>
+        <v>5272.81</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1084156-3249-CM25</t>
+          <t>4284-459-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7678,7 +8062,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7688,17 +8072,17 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>65.181.672-6</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7711,20 +8095,24 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>3012.75</v>
+        <v>5901.9</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1590-412-CM25</t>
+          <t>1084156-3249-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7749,17 +8137,17 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.301.000-9</t>
+          <t>65.181.672-6</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7772,20 +8160,24 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>4150.15</v>
+        <v>3012.75</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1590-410-CM25</t>
+          <t>1469-2728-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7805,48 +8197,52 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.301.000-9</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>15210.58</v>
+        <v>18092.26</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>3703-468-CM25</t>
+          <t>1590-410-CM25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7866,48 +8262,52 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>61.301.000-9</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>12255.11</v>
+        <v>15210.58</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>3843-203-CM25</t>
+          <t>1590-412-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7927,22 +8327,22 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>61.301.000-9</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7955,20 +8355,24 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>12804.17</v>
+        <v>4150.15</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1028871-1323-CM25</t>
+          <t>3703-468-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7988,17 +8392,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8008,28 +8412,32 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>10814.72</v>
+        <v>12255.11</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1057931-85-CM25</t>
+          <t>3843-203-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8049,48 +8457,52 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>38769.13</v>
+        <v>12804.17</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1213002-317-CM25</t>
+          <t>1028871-1323-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8110,48 +8522,52 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>70.880.300-6</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUCACION Y SAL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>12875.8</v>
+        <v>10814.72</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1590-408-CM25</t>
+          <t>1057931-85-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8176,43 +8592,47 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.301.000-9</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>4917.65</v>
+        <v>38769.13</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2756-213-CM25</t>
+          <t>1213002-317-CM25</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8237,27 +8657,27 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>70.880.300-6</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>CORP MUNICIPAL DE EDUCACION Y SAL</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8267,13 +8687,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>14458.26</v>
+        <v>12875.8</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2734-659-CM25</t>
+          <t>1590-408-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8293,17 +8713,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>61.301.000-9</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8313,28 +8733,32 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>5854.8</v>
+        <v>4917.65</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>188-838-CM25</t>
+          <t>2756-213-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8359,27 +8783,27 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8389,13 +8813,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>8170.8</v>
+        <v>14458.26</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>3675-105-CM25</t>
+          <t>2734-659-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8415,32 +8839,32 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>69.050.500-2</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PETORCA</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8450,13 +8874,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>2998.75</v>
+        <v>5854.8</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1213002-318-CM25</t>
+          <t>188-838-CM25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8481,12 +8905,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>70.880.300-6</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUCACION Y SAL</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8496,12 +8920,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.596.570-5</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8511,13 +8935,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>6961.26</v>
+        <v>8170.8</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>568963-231-CM25</t>
+          <t>3675-105-CM25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8532,7 +8956,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8542,43 +8966,47 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.979.610-1</t>
+          <t>69.050.500-2</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>COMISION DEL SISTEMA NACIONAL DE CERTIFICACION DE COMPETENCIAS LABORALES</t>
+          <t>I MUNICIPALIDAD DE PETORCA</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>3630.63</v>
+        <v>2998.75</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2854-1251-CM25</t>
+          <t>1213002-318-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8593,7 +9021,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8603,43 +9031,47 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>70.880.300-6</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>CORP MUNICIPAL DE EDUCACION Y SAL</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>7544.6</v>
+        <v>6961.26</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1432083-1327-CM25</t>
+          <t>568963-231-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8664,27 +9096,27 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.979.610-1</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>COMISION DEL SISTEMA NACIONAL DE CERTIFICACION DE COMPETENCIAS LABORALES</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.596.570-5</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8694,13 +9126,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>3071.34</v>
+        <v>3630.63</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1058758-262-CM25</t>
+          <t>2854-1251-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8725,43 +9157,47 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>30196.25</v>
+        <v>7544.6</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1214102-1718-CM25</t>
+          <t>1432083-1327-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8781,48 +9217,52 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>70.835.200-4</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE PUDAHUEL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr"/>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>26144.18</v>
+        <v>3071.34</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1426038-139-CM25</t>
+          <t>1058758-262-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8842,48 +9282,52 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>70.941.900-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social de Colina</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>11329.15</v>
+        <v>30196.25</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>586-502-CM25</t>
+          <t>1214102-1718-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8908,43 +9352,47 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>70.835.200-4</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>24111.07</v>
+        <v>26144.18</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2424-1914-CM25</t>
+          <t>1426038-139-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8969,17 +9417,17 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>70.941.900-5</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8992,20 +9440,24 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>8709.73</v>
+        <v>11329.15</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1426038-140-CM25</t>
+          <t>586-502-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9025,22 +9477,22 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>70.941.900-5</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social de Colina</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9053,20 +9505,24 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>11209.01</v>
+        <v>24111.07</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>4239-627-CM25</t>
+          <t>2424-1914-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9081,53 +9537,57 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>69.160.201-K</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>27654.65</v>
+        <v>8709.73</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1298354-368-CM25</t>
+          <t>1426038-140-CM25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9142,7 +9602,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9152,12 +9612,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>71.293.900-1</t>
+          <t>70.941.900-5</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9175,20 +9635,24 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>12769.72</v>
+        <v>11209.01</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2676-748-CM25</t>
+          <t>4239-627-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9213,43 +9677,47 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>69.255.500-7</t>
+          <t>69.160.201-K</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr"/>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>10602.66</v>
+        <v>27654.65</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2429-2610-CM25</t>
+          <t>1298354-368-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9269,48 +9737,52 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>71.293.900-1</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2584.68</v>
+        <v>12769.72</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1256505-228-CM25</t>
+          <t>2676-748-CM25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9335,43 +9807,47 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>71.015.300-0</t>
+          <t>69.255.500-7</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICENTE</t>
+          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>8815.040000000001</v>
+        <v>10602.66</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1300813-34-CM25</t>
+          <t>2429-2610-CM25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9391,48 +9867,52 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>70.913.100-1</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Corporación Comunal de Desarrollo Quinta Normal</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>59476.2</v>
+        <v>2584.68</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2013-1584-CM25</t>
+          <t>1256505-228-CM25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9457,27 +9937,27 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>71.015.300-0</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9487,13 +9967,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>34461.45</v>
+        <v>8815.040000000001</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2013-1583-CM25</t>
+          <t>1300813-34-CM25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9513,48 +9993,52 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>70.913.100-1</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>Corporación Comunal de Desarrollo Quinta Normal</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>8615.360000000001</v>
+        <v>59476.2</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5531-235-CM25</t>
+          <t>2013-1584-CM25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9574,48 +10058,52 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2186.61</v>
+        <v>34461.45</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>4291-1992-CM25</t>
+          <t>2013-1583-CM25</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9630,7 +10118,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9640,43 +10128,47 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>COMERCIAL FELP SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>76.427.199-8</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>3474.8</v>
+        <v>8615.360000000001</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>820-34-CM25</t>
+          <t>5531-235-CM25</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9691,7 +10183,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9701,43 +10193,47 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>3214.86</v>
+        <v>2186.61</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2292-1308-CM25</t>
+          <t>4291-1992-CM25</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9762,27 +10258,27 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMERCIAL FELP SPA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.427.199-8</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9792,13 +10288,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>11911.9</v>
+        <v>3474.8</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>4451-654-CM25</t>
+          <t>820-34-CM25</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9823,43 +10319,47 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>3859.17</v>
+        <v>3214.86</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1002588-274-CM25</t>
+          <t>2292-1308-CM25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9879,32 +10379,32 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.999.320-9</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -9914,13 +10414,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>9548.08</v>
+        <v>11911.9</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>4291-1964-CM25</t>
+          <t>4451-654-CM25</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9940,48 +10440,52 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>3451</v>
+        <v>3859.17</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3502-663-CM25</t>
+          <t>1002588-274-CM25</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10006,43 +10510,47 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>61.999.320-9</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>8513.26</v>
+        <v>9548.08</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1562-507-CM25</t>
+          <t>4291-1964-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10062,48 +10570,52 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>2449.02</v>
+        <v>3451</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1562-506-CM25</t>
+          <t>3502-663-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10128,43 +10640,47 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>69.180.700-2</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2221.02</v>
+        <v>8513.26</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1305525-95-CM25</t>
+          <t>1562-507-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10189,27 +10705,27 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.981.120-8</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE COSTA CENTRAL</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10219,13 +10735,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>5721.88</v>
+        <v>2449.02</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1561-271-CM25</t>
+          <t>1562-506-CM25</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10250,12 +10766,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.504.000-2</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10265,28 +10781,32 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>3153.48</v>
+        <v>2221.02</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>4494-609-CM25</t>
+          <t>1305525-95-CM25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10306,48 +10826,52 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>61.981.120-8</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE COSTA CENTRAL</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr"/>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>3730.65</v>
+        <v>5721.88</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1271357-146-CM25</t>
+          <t>1561-271-CM25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10372,12 +10896,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>70.954.200-1</t>
+          <t>61.504.000-2</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
+          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10387,12 +10911,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10402,13 +10926,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>59248.55</v>
+        <v>3153.48</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2934-92-CM25</t>
+          <t>4494-609-CM25</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10428,48 +10952,52 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>69.073.200-9</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALHUE</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>5142.11</v>
+        <v>3730.65</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>4291-2009-CM25</t>
+          <t>1271357-146-CM25</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10484,53 +11012,57 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>70.954.200-1</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>COMERCIAL FELP SPA</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>76.427.199-8</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr"/>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>2606.1</v>
+        <v>59248.55</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1232565-299-CM25</t>
+          <t>2934-92-CM25</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10545,7 +11077,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10555,27 +11087,27 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.073.200-9</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE ALHUE</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -10585,13 +11117,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>7651.76</v>
+        <v>5142.11</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2292-1314-CM25</t>
+          <t>4291-2009-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10606,7 +11138,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10616,27 +11148,27 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIAL FELP SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.427.199-8</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -10646,13 +11178,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>34981.94</v>
+        <v>2606.1</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1469-2832-CM25</t>
+          <t>1232565-299-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10667,37 +11199,37 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -10711,13 +11243,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>895962.9</v>
+        <v>7651.76</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2380-2074-CM25</t>
+          <t>2292-1314-CM25</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10742,27 +11274,27 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10772,13 +11304,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>3012.75</v>
+        <v>34981.94</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>4738-386-CM25</t>
+          <t>1469-2832-CM25</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10798,48 +11330,52 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr"/>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>8810.76</v>
+        <v>895962.9</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1347870-146-CM25</t>
+          <t>2380-2074-CM25</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10859,48 +11395,52 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>6409.04</v>
+        <v>3012.75</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1347870-145-CM25</t>
+          <t>4738-386-CM25</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10925,17 +11465,17 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10955,13 +11495,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>20835.71</v>
+        <v>8810.76</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2408-4466-CM25</t>
+          <t>1347870-146-CM25</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10986,43 +11526,47 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>8427.700000000001</v>
+        <v>6409.04</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2825-478-CM25</t>
+          <t>1347870-145-CM25</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11042,32 +11586,32 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -11077,6 +11621,136 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
+        <v>20835.71</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2408-4466-CM25</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>69.170.100-K</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="n">
+        <v>8427.700000000001</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2825-478-CM25</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>69.120.100-7</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="n">
         <v>2779.07</v>
       </c>
     </row>
